--- a/dados/excel/quadro_tempo_servico_secretaria.xlsx
+++ b/dados/excel/quadro_tempo_servico_secretaria.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$F$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
@@ -633,7 +633,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F173"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>1426441.02</v>
+        <v>1478933.1</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>17186.03638554217</v>
+        <v>16999.23103448276</v>
       </c>
     </row>
     <row r="3">
@@ -881,16 +881,16 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>26</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>1572018.06</v>
+        <v>1589319.43</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>5006.42694267516</v>
+        <v>5045.458507936508</v>
       </c>
     </row>
     <row r="5">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>17</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>2383489.62</v>
+        <v>2435589.75</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>8960.487293233084</v>
+        <v>9054.236988847584</v>
       </c>
     </row>
     <row r="7">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>90</v>
       </c>
       <c r="E8" s="11" t="n">
-        <v>4885062.62</v>
+        <v>4928693.25</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>4412.884028906956</v>
+        <v>4444.268034265104</v>
       </c>
     </row>
     <row r="9">
@@ -1001,16 +1001,16 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>177550.77</v>
+        <v>181296.14</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>3551.0154</v>
+        <v>3554.826274509804</v>
       </c>
     </row>
     <row r="10">
@@ -1025,16 +1025,16 @@
         </is>
       </c>
       <c r="C10" s="10" t="n">
-        <v>987</v>
+        <v>1004</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>22</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>4376234.8</v>
+        <v>4474846.81</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4433.875177304964</v>
+        <v>4457.018735059761</v>
       </c>
     </row>
     <row r="11">
@@ -1049,16 +1049,16 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>929</v>
+        <v>946</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>21</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>4465333.41</v>
+        <v>4566218.59</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>4806.602163616792</v>
+        <v>4826.869545454545</v>
       </c>
     </row>
     <row r="12">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>1033</v>
+        <v>1053</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>24</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>4851055.91</v>
+        <v>4962054.85</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>4696.085101645693</v>
+        <v>4712.302801519468</v>
       </c>
     </row>
     <row r="13">
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>21</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>3344622.61</v>
+        <v>3412665.07</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>4717.380267983074</v>
+        <v>4733.238654646324</v>
       </c>
     </row>
     <row r="14">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1104</v>
+        <v>1123</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>28</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>4747386.82</v>
+        <v>4856136.96</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4300.169221014493</v>
+        <v>4324.25374888691</v>
       </c>
     </row>
     <row r="15">
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>6476</v>
+        <v>6566</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>197</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>32476128.48</v>
+        <v>33058872.44</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>5014.843804817789</v>
+        <v>5034.857209869023</v>
       </c>
     </row>
     <row r="16">
@@ -1169,16 +1169,16 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>4337</v>
+        <v>4475</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>24843996.03</v>
+        <v>25741995.11</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5728.382759972332</v>
+        <v>5752.401141899441</v>
       </c>
     </row>
     <row r="17">
@@ -1193,16 +1193,16 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>1914</v>
+        <v>1958</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>12405315.9</v>
+        <v>12788840.44</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>6481.356269592477</v>
+        <v>6531.583472931563</v>
       </c>
     </row>
     <row r="18">
@@ -1217,16 +1217,16 @@
         </is>
       </c>
       <c r="C18" s="10" t="n">
-        <v>6907</v>
+        <v>7013</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>47625324.64</v>
+        <v>48638004.17</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6895.225805704358</v>
+        <v>6935.406269784686</v>
       </c>
     </row>
     <row r="19">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>2237</v>
+        <v>2273</v>
       </c>
       <c r="D19" s="14" t="n">
         <v>44</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>21904045.32</v>
+        <v>22377496.51</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>9791.705552078676</v>
+        <v>9844.917074351079</v>
       </c>
     </row>
     <row r="20">
@@ -1265,16 +1265,16 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>322183.35</v>
+        <v>342260.58</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>17899.075</v>
+        <v>18013.71473684211</v>
       </c>
     </row>
     <row r="21">
@@ -1285,44 +1285,44 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>3136</v>
+        <v>2</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>27167766.43</v>
+        <v>30399.65</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>8663.190825892858</v>
+        <v>15199.825</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Educação</t>
+          <t>Secretaria da Cidadania</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>123271</v>
+        <v>3146</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>5234</v>
+        <v>148</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>502584151.29</v>
+        <v>27338951.1</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4077.067203884125</v>
+        <v>8690.067101080738</v>
       </c>
     </row>
     <row r="23">
@@ -1333,20 +1333,20 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C23" s="14" t="n">
-        <v>79462</v>
+        <v>126966</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>2058</v>
+        <v>5581</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>389861598.05</v>
+        <v>519708362.87</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>4906.264605094259</v>
+        <v>4093.287674416773</v>
       </c>
     </row>
     <row r="24">
@@ -1357,20 +1357,20 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>122823</v>
+        <v>81032</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>2933</v>
+        <v>2150</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>748849876.1</v>
+        <v>400004618.26</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6096.984083599978</v>
+        <v>4936.378446292822</v>
       </c>
     </row>
     <row r="25">
@@ -1381,20 +1381,20 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>65530</v>
+        <v>124760</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>1396</v>
+        <v>2981</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>505839490.74</v>
+        <v>765191016.88</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>7719.204802990997</v>
+        <v>6133.304078871433</v>
       </c>
     </row>
     <row r="26">
@@ -1405,20 +1405,20 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>30996</v>
+        <v>66548</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>833</v>
+        <v>1403</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>252597146.35</v>
+        <v>517090678.75</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>8149.34657213834</v>
+        <v>7770.191121446174</v>
       </c>
     </row>
     <row r="27">
@@ -1429,20 +1429,20 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>2891</v>
+        <v>31485</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>112</v>
+        <v>840</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>22375958.95</v>
+        <v>257902779.34</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>7739.868194396402</v>
+        <v>8191.290434810227</v>
       </c>
     </row>
     <row r="28">
@@ -1453,44 +1453,44 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>64745</v>
+        <v>2942</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>5225</v>
+        <v>112</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>256451562.46</v>
+        <v>22867624.88</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3960.947755965712</v>
+        <v>7772.816070700203</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Secretaria da Fazenda</t>
+          <t>Secretaria da Educação</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>963</v>
+        <v>64852</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>34</v>
+        <v>5289</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>4665816.1</v>
+        <v>258451174.31</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>4845.084215991692</v>
+        <v>3985.246011071362</v>
       </c>
     </row>
     <row r="30">
@@ -1501,20 +1501,20 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C30" s="10" t="n">
-        <v>2543</v>
+        <v>990</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>16041657.36</v>
+        <v>4863225.79</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6308.162548171451</v>
+        <v>4912.349282828282</v>
       </c>
     </row>
     <row r="31">
@@ -1525,20 +1525,20 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>2809</v>
+        <v>2581</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>19310089.14</v>
+        <v>16466890.91</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>6874.364236383055</v>
+        <v>6380.042971716389</v>
       </c>
     </row>
     <row r="32">
@@ -1549,20 +1549,20 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>4599</v>
+        <v>2848</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>52686527.3</v>
+        <v>19765650.89</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>11456.08334420526</v>
+        <v>6940.186408005618</v>
       </c>
     </row>
     <row r="33">
@@ -1573,20 +1573,20 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>69</v>
+        <v>4666</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>335825.42</v>
+        <v>53923476.76</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>4867.035072463768</v>
+        <v>11556.68168881269</v>
       </c>
     </row>
     <row r="34">
@@ -1597,44 +1597,44 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C34" s="10" t="n">
-        <v>1849</v>
+        <v>70</v>
       </c>
       <c r="D34" s="10" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>16712207.96</v>
+        <v>344695.95</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>9038.511606273662</v>
+        <v>4924.227857142857</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Secretaria da Habitação e Regularização Fundiária</t>
+          <t>Secretaria da Fazenda</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>564</v>
+        <v>1856</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>18</v>
+        <v>109</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>4662090.72</v>
+        <v>16845584.74</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>8266.118297872339</v>
+        <v>9076.284881465517</v>
       </c>
     </row>
     <row r="36">
@@ -1645,20 +1645,20 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>294</v>
+        <v>579</v>
       </c>
       <c r="D36" s="10" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>2416257.88</v>
+        <v>4807761.94</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>8218.564217687075</v>
+        <v>8303.561208981002</v>
       </c>
     </row>
     <row r="37">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>652</v>
+        <v>298</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>5415024.8</v>
+        <v>2456863.32</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>8305.252760736195</v>
+        <v>8244.507785234899</v>
       </c>
     </row>
     <row r="38">
@@ -1693,20 +1693,20 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>581</v>
+        <v>665</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>6435643.19</v>
+        <v>5542513.58</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>11076.83853700516</v>
+        <v>8334.606887218046</v>
       </c>
     </row>
     <row r="39">
@@ -1717,44 +1717,44 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>542</v>
+        <v>593</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>2542288.52</v>
+        <v>6597010.85</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>4690.569225092251</v>
+        <v>11124.80750421585</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Mulher</t>
+          <t>Secretaria da Habitação e Regularização Fundiária</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C40" s="10" t="n">
-        <v>101</v>
+        <v>542</v>
       </c>
       <c r="D40" s="10" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E40" s="11" t="n">
-        <v>1336570.13</v>
+        <v>2542288.52</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>13233.36762376238</v>
+        <v>4690.569225092251</v>
       </c>
     </row>
     <row r="41">
@@ -1765,20 +1765,20 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C41" s="14" t="n">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>754154.87</v>
+        <v>1395017.31</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>12782.28593220339</v>
+        <v>12567.72351351351</v>
       </c>
     </row>
     <row r="42">
@@ -1789,20 +1789,20 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>824744.8199999999</v>
+        <v>56069.87</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>24257.20058823529</v>
+        <v>18689.95666666667</v>
       </c>
     </row>
     <row r="43">
@@ -1813,68 +1813,68 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C43" s="14" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>699521.9500000001</v>
+        <v>783893.8100000001</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>19986.34142857143</v>
+        <v>12850.71819672131</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>27567</v>
+        <v>36</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>1060</v>
+        <v>2</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>195272185.39</v>
+        <v>840537.23</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>7083.548641128886</v>
+        <v>23348.25638888889</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C45" s="14" t="n">
-        <v>8872</v>
+        <v>36</v>
       </c>
       <c r="D45" s="14" t="n">
-        <v>175</v>
+        <v>6</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>64858129.51</v>
+        <v>716633.28</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>7310.429385707845</v>
+        <v>19906.48</v>
       </c>
     </row>
     <row r="46">
@@ -1885,20 +1885,20 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>59901</v>
+        <v>28613</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>889</v>
+        <v>1077</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>446347086.46</v>
+        <v>203278425.11</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>7451.412939016042</v>
+        <v>7104.407965260546</v>
       </c>
     </row>
     <row r="47">
@@ -1909,20 +1909,20 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C47" s="14" t="n">
-        <v>44143</v>
+        <v>9123</v>
       </c>
       <c r="D47" s="14" t="n">
-        <v>650</v>
+        <v>255</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>467509605.93</v>
+        <v>67150559.31999999</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>10590.79822236821</v>
+        <v>7360.578682450948</v>
       </c>
     </row>
     <row r="48">
@@ -1933,20 +1933,20 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>15452</v>
+        <v>60789</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>232</v>
+        <v>890</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>208445691.98</v>
+        <v>454999917.25</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>13489.88428552938</v>
+        <v>7484.905447531626</v>
       </c>
     </row>
     <row r="49">
@@ -1957,20 +1957,20 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C49" s="14" t="n">
-        <v>2772</v>
+        <v>44810</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>49</v>
+        <v>651</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>50735507.09</v>
+        <v>476594954.49</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>18302.85248556999</v>
+        <v>10635.90614795805</v>
       </c>
     </row>
     <row r="50">
@@ -1981,68 +1981,68 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>23757</v>
+        <v>15684</v>
       </c>
       <c r="D50" s="10" t="n">
-        <v>1050</v>
+        <v>232</v>
       </c>
       <c r="E50" s="11" t="n">
-        <v>268984479.29</v>
+        <v>212285585.24</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>11322.32517952603</v>
+        <v>13535.16865850548</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C51" s="14" t="n">
-        <v>1925</v>
+        <v>2813</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>9721664.01</v>
+        <v>51583045</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>5050.21507012987</v>
+        <v>18337.37824386776</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>1647</v>
+        <v>23868</v>
       </c>
       <c r="D52" s="10" t="n">
-        <v>32</v>
+        <v>1067</v>
       </c>
       <c r="E52" s="11" t="n">
-        <v>12251790.42</v>
+        <v>271233175.35</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>7438.852714025501</v>
+        <v>11363.88366641529</v>
       </c>
     </row>
     <row r="53">
@@ -2053,20 +2053,20 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C53" s="14" t="n">
-        <v>4937</v>
+        <v>1964</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>37485700.09</v>
+        <v>9900743.49</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>7592.809416649788</v>
+        <v>5041.111756619145</v>
       </c>
     </row>
     <row r="54">
@@ -2077,20 +2077,20 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>1883</v>
+        <v>1676</v>
       </c>
       <c r="D54" s="10" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E54" s="11" t="n">
-        <v>16207748.74</v>
+        <v>12546631.01</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>8607.40772172066</v>
+        <v>7486.056688544152</v>
       </c>
     </row>
     <row r="55">
@@ -2101,20 +2101,20 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C55" s="14" t="n">
-        <v>3</v>
+        <v>4988</v>
       </c>
       <c r="D55" s="14" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>62422.93</v>
+        <v>38072954.34</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>20807.64333333333</v>
+        <v>7632.909851643946</v>
       </c>
     </row>
     <row r="56">
@@ -2125,20 +2125,20 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C56" s="10" t="n">
-        <v>49</v>
+        <v>1900</v>
       </c>
       <c r="D56" s="10" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E56" s="11" t="n">
-        <v>763101.61</v>
+        <v>16445689.22</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>15573.50224489796</v>
+        <v>8655.625905263158</v>
       </c>
     </row>
     <row r="57">
@@ -2149,68 +2149,68 @@
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C57" s="14" t="n">
-        <v>5783</v>
+        <v>3</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>331</v>
+        <v>2</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>35297507.45</v>
+        <v>62422.93</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>6103.667205602629</v>
+        <v>20807.64333333333</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>1828</v>
+        <v>49</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>22508953.26</v>
+        <v>763101.61</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>12313.43176148797</v>
+        <v>15573.50224489796</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C59" s="14" t="n">
-        <v>1854</v>
+        <v>5813</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>37</v>
+        <v>335</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>27538205.92</v>
+        <v>35615493.87</v>
       </c>
       <c r="F59" s="15" t="n">
-        <v>14853.40125134844</v>
+        <v>6126.869752279374</v>
       </c>
     </row>
     <row r="60">
@@ -2221,20 +2221,20 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>2244</v>
+        <v>1889</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>29791776.55</v>
+        <v>23277300.27</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>13276.19275846702</v>
+        <v>12322.55175754367</v>
       </c>
     </row>
     <row r="61">
@@ -2245,20 +2245,20 @@
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C61" s="14" t="n">
-        <v>1384</v>
+        <v>1884</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>22297172.46</v>
+        <v>28243252.09</v>
       </c>
       <c r="F61" s="15" t="n">
-        <v>16110.67374277457</v>
+        <v>14991.11045116773</v>
       </c>
     </row>
     <row r="62">
@@ -2269,20 +2269,20 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>10</v>
+        <v>2276</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>90817.42999999999</v>
+        <v>30344135.7</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>9081.742999999999</v>
+        <v>13332.22130931459</v>
       </c>
     </row>
     <row r="63">
@@ -2293,68 +2293,68 @@
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C63" s="14" t="n">
-        <v>1619</v>
+        <v>1404</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>124</v>
+        <v>27</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>24750632.08</v>
+        <v>22750612.14</v>
       </c>
       <c r="F63" s="15" t="n">
-        <v>15287.60474366893</v>
+        <v>16204.1397008547</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C64" s="10" t="n">
-        <v>316</v>
+        <v>10</v>
       </c>
       <c r="D64" s="10" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E64" s="11" t="n">
-        <v>2740735.4</v>
+        <v>90817.42999999999</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>8673.21329113924</v>
+        <v>9081.742999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C65" s="14" t="n">
-        <v>360</v>
+        <v>1623</v>
       </c>
       <c r="D65" s="14" t="n">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="E65" s="15" t="n">
-        <v>3293533.05</v>
+        <v>24893237.64</v>
       </c>
       <c r="F65" s="15" t="n">
-        <v>9148.702916666665</v>
+        <v>15337.79275415897</v>
       </c>
     </row>
     <row r="66">
@@ -2365,20 +2365,20 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>402</v>
+        <v>334</v>
       </c>
       <c r="D66" s="10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E66" s="11" t="n">
-        <v>3944210.66</v>
+        <v>2885883.92</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>9811.469303482587</v>
+        <v>8640.371017964071</v>
       </c>
     </row>
     <row r="67">
@@ -2389,20 +2389,20 @@
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C67" s="14" t="n">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D67" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>3824113.45</v>
+        <v>3381691.25</v>
       </c>
       <c r="F67" s="15" t="n">
-        <v>10505.80618131868</v>
+        <v>9239.593579234972</v>
       </c>
     </row>
     <row r="68">
@@ -2413,68 +2413,68 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>644</v>
+        <v>407</v>
       </c>
       <c r="D68" s="10" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>5961760.25</v>
+        <v>4026756.96</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>9257.391692546584</v>
+        <v>9893.751744471745</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C69" s="14" t="n">
-        <v>604</v>
+        <v>369</v>
       </c>
       <c r="D69" s="14" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>3901602.65</v>
+        <v>3887002.91</v>
       </c>
       <c r="F69" s="15" t="n">
-        <v>6459.607036423841</v>
+        <v>10533.88322493225</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>277</v>
+        <v>646</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>852252.8</v>
+        <v>5984356.02</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3076.724909747293</v>
+        <v>9263.709009287924</v>
       </c>
     </row>
     <row r="71">
@@ -2485,20 +2485,20 @@
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C71" s="14" t="n">
-        <v>1447</v>
+        <v>637</v>
       </c>
       <c r="D71" s="14" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>10318824.95</v>
+        <v>4079927.12</v>
       </c>
       <c r="F71" s="15" t="n">
-        <v>7131.185176226675</v>
+        <v>6404.909136577709</v>
       </c>
     </row>
     <row r="72">
@@ -2509,20 +2509,20 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>2163722.64</v>
+        <v>925621.84</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>6957.307524115756</v>
+        <v>3169.937808219178</v>
       </c>
     </row>
     <row r="73">
@@ -2533,68 +2533,68 @@
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C73" s="14" t="n">
-        <v>1992</v>
+        <v>1464</v>
       </c>
       <c r="D73" s="14" t="n">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>10623431.94</v>
+        <v>10475334.08</v>
       </c>
       <c r="F73" s="15" t="n">
-        <v>5333.048162650603</v>
+        <v>7155.282841530055</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>1936313.97</v>
+        <v>2269120.88</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>6226.089935691318</v>
+        <v>7113.231598746082</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C75" s="14" t="n">
-        <v>704</v>
+        <v>1999</v>
       </c>
       <c r="D75" s="14" t="n">
-        <v>24</v>
+        <v>130</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>2681182.46</v>
+        <v>10698072.23</v>
       </c>
       <c r="F75" s="15" t="n">
-        <v>3808.4978125</v>
+        <v>5351.711970985493</v>
       </c>
     </row>
     <row r="76">
@@ -2605,20 +2605,20 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C76" s="10" t="n">
-        <v>602</v>
+        <v>318</v>
       </c>
       <c r="D76" s="10" t="n">
         <v>21</v>
       </c>
       <c r="E76" s="11" t="n">
-        <v>5206581.14</v>
+        <v>1960882.7</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>8648.805880398671</v>
+        <v>6166.297798742138</v>
       </c>
     </row>
     <row r="77">
@@ -2629,20 +2629,20 @@
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C77" s="14" t="n">
-        <v>515</v>
+        <v>710</v>
       </c>
       <c r="D77" s="14" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>4238292.77</v>
+        <v>2764927.35</v>
       </c>
       <c r="F77" s="15" t="n">
-        <v>8229.694699029125</v>
+        <v>3894.263873239437</v>
       </c>
     </row>
     <row r="78">
@@ -2653,20 +2653,20 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>100</v>
+        <v>604</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>597641.09</v>
+        <v>5245068.24</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>5976.4109</v>
+        <v>8683.887814569536</v>
       </c>
     </row>
     <row r="79">
@@ -2677,68 +2677,68 @@
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C79" s="14" t="n">
-        <v>2015</v>
+        <v>520</v>
       </c>
       <c r="D79" s="14" t="n">
-        <v>164</v>
+        <v>15</v>
       </c>
       <c r="E79" s="15" t="n">
-        <v>14193758.96</v>
+        <v>4313180.11</v>
       </c>
       <c r="F79" s="15" t="n">
-        <v>7044.049111662532</v>
+        <v>8294.577134615385</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D80" s="10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E80" s="11" t="n">
-        <v>1028774.47</v>
+        <v>597641.09</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>8230.195760000001</v>
+        <v>5976.4109</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C81" s="14" t="n">
-        <v>114</v>
+        <v>2015</v>
       </c>
       <c r="D81" s="14" t="n">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>1169691.87</v>
+        <v>14193758.96</v>
       </c>
       <c r="F81" s="15" t="n">
-        <v>10260.455</v>
+        <v>7044.049111662532</v>
       </c>
     </row>
     <row r="82">
@@ -2749,20 +2749,20 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>112</v>
+        <v>135</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>748996.04</v>
+        <v>1151131.12</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>6687.464642857143</v>
+        <v>8526.897185185186</v>
       </c>
     </row>
     <row r="83">
@@ -2773,20 +2773,20 @@
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C83" s="14" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>1127107.02</v>
+        <v>1257870.84</v>
       </c>
       <c r="F83" s="15" t="n">
-        <v>9633.393333333333</v>
+        <v>10062.96672</v>
       </c>
     </row>
     <row r="84">
@@ -2797,68 +2797,68 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C84" s="10" t="n">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="D84" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E84" s="11" t="n">
-        <v>804274.37</v>
+        <v>791204.48</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>16413.76265306123</v>
+        <v>6648.777142857142</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C85" s="14" t="n">
-        <v>1054</v>
+        <v>123</v>
       </c>
       <c r="D85" s="14" t="n">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>6710874</v>
+        <v>1189354.46</v>
       </c>
       <c r="F85" s="15" t="n">
-        <v>6367.053130929791</v>
+        <v>9669.548455284552</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>516</v>
+        <v>49</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E86" s="11" t="n">
-        <v>2533751.12</v>
+        <v>804274.37</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>4910.370387596899</v>
+        <v>16413.76265306123</v>
       </c>
     </row>
     <row r="87">
@@ -2869,20 +2869,20 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C87" s="14" t="n">
-        <v>1408</v>
+        <v>1103</v>
       </c>
       <c r="D87" s="14" t="n">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>10641004.35</v>
+        <v>7084581.43</v>
       </c>
       <c r="F87" s="15" t="n">
-        <v>7557.531498579545</v>
+        <v>6423.011269265638</v>
       </c>
     </row>
     <row r="88">
@@ -2893,20 +2893,20 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C88" s="10" t="n">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="D88" s="10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>5481082.78</v>
+        <v>2618681.31</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>10726.18939334638</v>
+        <v>4969.034743833017</v>
       </c>
     </row>
     <row r="89">
@@ -2917,68 +2917,68 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C89" s="14" t="n">
-        <v>2384</v>
+        <v>1433</v>
       </c>
       <c r="D89" s="14" t="n">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>24816101.31</v>
+        <v>10873896.19</v>
       </c>
       <c r="F89" s="15" t="n">
-        <v>10409.43846895973</v>
+        <v>7588.203900907188</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>1284</v>
+        <v>516</v>
       </c>
       <c r="D90" s="10" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>7461512.81</v>
+        <v>5546767.8</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>5811.147048286604</v>
+        <v>10749.55</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C91" s="14" t="n">
-        <v>616</v>
+        <v>2399</v>
       </c>
       <c r="D91" s="14" t="n">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>5934891.89</v>
+        <v>25224555.14</v>
       </c>
       <c r="F91" s="15" t="n">
-        <v>9634.564756493506</v>
+        <v>10514.61239683201</v>
       </c>
     </row>
     <row r="92">
@@ -2989,20 +2989,20 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C92" s="10" t="n">
-        <v>2259</v>
+        <v>1358</v>
       </c>
       <c r="D92" s="10" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>20835162.76</v>
+        <v>7894075.81</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>9223.179619300576</v>
+        <v>5813.016060382915</v>
       </c>
     </row>
     <row r="93">
@@ -3013,20 +3013,20 @@
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C93" s="14" t="n">
-        <v>1138</v>
+        <v>642</v>
       </c>
       <c r="D93" s="14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E93" s="15" t="n">
-        <v>14637414.22</v>
+        <v>6182493.43</v>
       </c>
       <c r="F93" s="15" t="n">
-        <v>12862.40265377856</v>
+        <v>9630.052071651089</v>
       </c>
     </row>
     <row r="94">
@@ -3037,20 +3037,20 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>181</v>
+        <v>2310</v>
       </c>
       <c r="D94" s="10" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>3339737.53</v>
+        <v>21457216.69</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>18451.58856353591</v>
+        <v>9288.838393939395</v>
       </c>
     </row>
     <row r="95">
@@ -3061,20 +3061,20 @@
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C95" s="14" t="n">
-        <v>27</v>
+        <v>1157</v>
       </c>
       <c r="D95" s="14" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E95" s="15" t="n">
-        <v>558726.4</v>
+        <v>14928559.09</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>20693.57037037037</v>
+        <v>12902.81684528954</v>
       </c>
     </row>
     <row r="96">
@@ -3085,68 +3085,68 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>1207</v>
+        <v>183</v>
       </c>
       <c r="D96" s="10" t="n">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>13505831.4</v>
+        <v>3390193.23</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>11189.58690969345</v>
+        <v>18525.64606557377</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C97" s="14" t="n">
-        <v>1344</v>
+        <v>28</v>
       </c>
       <c r="D97" s="14" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>11222165.97</v>
+        <v>584316.48</v>
       </c>
       <c r="F97" s="15" t="n">
-        <v>8349.825870535715</v>
+        <v>20868.44571428571</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C98" s="10" t="n">
-        <v>603</v>
+        <v>1213</v>
       </c>
       <c r="D98" s="10" t="n">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>4962896.04</v>
+        <v>13649368.15</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>8230.341691542289</v>
+        <v>11252.57061005771</v>
       </c>
     </row>
     <row r="99">
@@ -3157,20 +3157,20 @@
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C99" s="14" t="n">
-        <v>1557</v>
+        <v>1405</v>
       </c>
       <c r="D99" s="14" t="n">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="E99" s="15" t="n">
-        <v>21066695.18</v>
+        <v>11763443.78</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>13530.3116120745</v>
+        <v>8372.557850533807</v>
       </c>
     </row>
     <row r="100">
@@ -3181,20 +3181,20 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>936</v>
+        <v>621</v>
       </c>
       <c r="D100" s="10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>11648143.8</v>
+        <v>5149628.36</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>12444.59807692308</v>
+        <v>8292.477230273753</v>
       </c>
     </row>
     <row r="101">
@@ -3205,20 +3205,20 @@
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C101" s="14" t="n">
-        <v>175</v>
+        <v>1591</v>
       </c>
       <c r="D101" s="14" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="E101" s="15" t="n">
-        <v>3097586.57</v>
+        <v>21722367.95</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>17700.49468571429</v>
+        <v>13653.27966687618</v>
       </c>
     </row>
     <row r="102">
@@ -3229,20 +3229,20 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="D102" s="10" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>997982.76</v>
+        <v>11850060.59</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>11740.97364705882</v>
+        <v>12473.74798947368</v>
       </c>
     </row>
     <row r="103">
@@ -3253,68 +3253,68 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C103" s="14" t="n">
-        <v>2847</v>
+        <v>177</v>
       </c>
       <c r="D103" s="14" t="n">
-        <v>298</v>
+        <v>7</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>23784469.37</v>
+        <v>3125252.7</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>8354.221766772042</v>
+        <v>17656.79491525424</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C104" s="10" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="D104" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>209004.38</v>
+        <v>1029180.65</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>5097.667804878049</v>
+        <v>11829.66264367816</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C105" s="14" t="n">
-        <v>49</v>
+        <v>2851</v>
       </c>
       <c r="D105" s="14" t="n">
-        <v>4</v>
+        <v>298</v>
       </c>
       <c r="E105" s="15" t="n">
-        <v>728334.46</v>
+        <v>23836161.28</v>
       </c>
       <c r="F105" s="15" t="n">
-        <v>14863.96857142857</v>
+        <v>8360.631806383726</v>
       </c>
     </row>
     <row r="106">
@@ -3325,20 +3325,20 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D106" s="10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>677323.35</v>
+        <v>270792.13</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>9960.637499999999</v>
+        <v>5641.502708333333</v>
       </c>
     </row>
     <row r="107">
@@ -3349,68 +3349,68 @@
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C107" s="14" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="D107" s="14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>1442003.67</v>
+        <v>791534.86</v>
       </c>
       <c r="F107" s="15" t="n">
-        <v>15673.95293478261</v>
+        <v>14934.62</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>561</v>
+        <v>71</v>
       </c>
       <c r="D108" s="10" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="E108" s="11" t="n">
-        <v>3146505.91</v>
+        <v>718280.09</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>5608.744937611408</v>
+        <v>10116.62098591549</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C109" s="14" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D109" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E109" s="15" t="n">
-        <v>210086.24</v>
+        <v>1442003.67</v>
       </c>
       <c r="F109" s="15" t="n">
-        <v>2728.392727272727</v>
+        <v>15673.95293478261</v>
       </c>
     </row>
     <row r="110">
@@ -3421,20 +3421,20 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>419</v>
+        <v>605</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="E110" s="11" t="n">
-        <v>3844092.15</v>
+        <v>3413027.12</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>9174.444272076373</v>
+        <v>5641.367140495868</v>
       </c>
     </row>
     <row r="111">
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C111" s="14" t="n">
-        <v>149</v>
+        <v>82</v>
       </c>
       <c r="D111" s="14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>1791899.36</v>
+        <v>222898.48</v>
       </c>
       <c r="F111" s="15" t="n">
-        <v>12026.17020134228</v>
+        <v>2718.274146341464</v>
       </c>
     </row>
     <row r="112">
@@ -3469,20 +3469,20 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C112" s="10" t="n">
-        <v>54</v>
+        <v>430</v>
       </c>
       <c r="D112" s="10" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E112" s="11" t="n">
-        <v>543790.22</v>
+        <v>3956678.57</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>10070.18925925926</v>
+        <v>9201.578069767442</v>
       </c>
     </row>
     <row r="113">
@@ -3493,20 +3493,20 @@
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C113" s="14" t="n">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="D113" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>1385100.33</v>
+        <v>1854700.34</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>13990.91242424242</v>
+        <v>12122.22444444444</v>
       </c>
     </row>
     <row r="114">
@@ -3517,68 +3517,68 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>962</v>
+        <v>55</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E114" s="11" t="n">
-        <v>8512431.33</v>
+        <v>558282.5</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>8848.681216216217</v>
+        <v>10150.59090909091</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C115" s="14" t="n">
-        <v>610</v>
+        <v>104</v>
       </c>
       <c r="D115" s="14" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="E115" s="15" t="n">
-        <v>5514748.64</v>
+        <v>1465485.73</v>
       </c>
       <c r="F115" s="15" t="n">
-        <v>9040.571540983607</v>
+        <v>14091.20894230769</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C116" s="10" t="n">
-        <v>52</v>
+        <v>967</v>
       </c>
       <c r="D116" s="10" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="E116" s="11" t="n">
-        <v>497225.09</v>
+        <v>8560284.48</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>9562.020961538463</v>
+        <v>8852.414146845917</v>
       </c>
     </row>
     <row r="117">
@@ -3589,20 +3589,20 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C117" s="14" t="n">
-        <v>150</v>
+        <v>649</v>
       </c>
       <c r="D117" s="14" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="E117" s="15" t="n">
-        <v>1408799.3</v>
+        <v>5887213.36</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>9391.995333333334</v>
+        <v>9071.207026194146</v>
       </c>
     </row>
     <row r="118">
@@ -3613,20 +3613,20 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>213</v>
+        <v>56</v>
       </c>
       <c r="D118" s="10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E118" s="11" t="n">
-        <v>2538346.49</v>
+        <v>515260.72</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>11917.1196713615</v>
+        <v>9201.084285714287</v>
       </c>
     </row>
     <row r="119">
@@ -3637,68 +3637,68 @@
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C119" s="14" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D119" s="14" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E119" s="15" t="n">
-        <v>1118944.29</v>
+        <v>1522759.63</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>6740.628253012049</v>
+        <v>9577.104591194968</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>2335</v>
+        <v>221</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="E120" s="11" t="n">
-        <v>14583749.95</v>
+        <v>2700860.4</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>6245.717323340471</v>
+        <v>12221.08778280543</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C121" s="14" t="n">
-        <v>884</v>
+        <v>168</v>
       </c>
       <c r="D121" s="14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E121" s="15" t="n">
-        <v>5447409.05</v>
+        <v>1152374.13</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>6162.227432126697</v>
+        <v>6859.369821428571</v>
       </c>
     </row>
     <row r="122">
@@ -3709,20 +3709,20 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>1947</v>
+        <v>2418</v>
       </c>
       <c r="D122" s="10" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="E122" s="11" t="n">
-        <v>17651867.54</v>
+        <v>15129249.22</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>9066.187745249101</v>
+        <v>6256.926889991729</v>
       </c>
     </row>
     <row r="123">
@@ -3733,20 +3733,20 @@
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C123" s="14" t="n">
-        <v>1846</v>
+        <v>906</v>
       </c>
       <c r="D123" s="14" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E123" s="15" t="n">
-        <v>14894081.47</v>
+        <v>5601877.19</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>8068.299821235103</v>
+        <v>6183.087406181015</v>
       </c>
     </row>
     <row r="124">
@@ -3757,20 +3757,20 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>3</v>
+        <v>1987</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E124" s="11" t="n">
-        <v>42115.82</v>
+        <v>18081430.07</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>14038.60666666667</v>
+        <v>9099.864151987922</v>
       </c>
     </row>
     <row r="125">
@@ -3781,20 +3781,20 @@
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C125" s="14" t="n">
-        <v>286</v>
+        <v>1876</v>
       </c>
       <c r="D125" s="14" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="E125" s="15" t="n">
-        <v>3318165.88</v>
+        <v>15267054.4</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>11601.9786013986</v>
+        <v>8138.088699360342</v>
       </c>
     </row>
     <row r="126">
@@ -3805,68 +3805,68 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>3044</v>
+        <v>3</v>
       </c>
       <c r="D126" s="10" t="n">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="E126" s="11" t="n">
-        <v>23010851.8</v>
+        <v>42115.82</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>7559.412549277267</v>
+        <v>14038.60666666667</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C127" s="14" t="n">
-        <v>1449</v>
+        <v>291</v>
       </c>
       <c r="D127" s="14" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>7588389.51</v>
+        <v>3405544.95</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>5236.983788819875</v>
+        <v>11702.90360824742</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>1085</v>
+        <v>3059</v>
       </c>
       <c r="D128" s="10" t="n">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>7305670.5</v>
+        <v>23262401.07</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>6733.336866359447</v>
+        <v>7604.577008826414</v>
       </c>
     </row>
     <row r="129">
@@ -3877,20 +3877,20 @@
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C129" s="14" t="n">
-        <v>2667</v>
+        <v>1497</v>
       </c>
       <c r="D129" s="14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E129" s="15" t="n">
-        <v>19677814.69</v>
+        <v>7860909.86</v>
       </c>
       <c r="F129" s="15" t="n">
-        <v>7378.258226471691</v>
+        <v>5251.108790915164</v>
       </c>
     </row>
     <row r="130">
@@ -3901,20 +3901,20 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>1850</v>
+        <v>1106</v>
       </c>
       <c r="D130" s="10" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>18818074.65</v>
+        <v>7540515.06</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>10171.93224324324</v>
+        <v>6817.82555153707</v>
       </c>
     </row>
     <row r="131">
@@ -3925,20 +3925,20 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C131" s="14" t="n">
-        <v>75</v>
+        <v>2705</v>
       </c>
       <c r="D131" s="14" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>1243975.97</v>
+        <v>20091671.25</v>
       </c>
       <c r="F131" s="15" t="n">
-        <v>16586.34626666667</v>
+        <v>7427.604898336414</v>
       </c>
     </row>
     <row r="132">
@@ -3949,68 +3949,68 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>1225</v>
+        <v>1879</v>
       </c>
       <c r="D132" s="10" t="n">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>5674497.65</v>
+        <v>19193236.09</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>4632.242979591837</v>
+        <v>10214.60143161256</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C133" s="14" t="n">
-        <v>29</v>
+        <v>76</v>
       </c>
       <c r="D133" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>375351.39</v>
+        <v>1268008.74</v>
       </c>
       <c r="F133" s="15" t="n">
-        <v>12943.15137931035</v>
+        <v>16684.32552631579</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C134" s="10" t="n">
-        <v>89</v>
+        <v>1227</v>
       </c>
       <c r="D134" s="10" t="n">
-        <v>5</v>
+        <v>126</v>
       </c>
       <c r="E134" s="11" t="n">
-        <v>707834.27</v>
+        <v>5676161.57</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>7953.194044943821</v>
+        <v>4626.048549307254</v>
       </c>
     </row>
     <row r="135">
@@ -4021,20 +4021,20 @@
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C135" s="14" t="n">
-        <v>164</v>
+        <v>30</v>
       </c>
       <c r="D135" s="14" t="n">
         <v>5</v>
       </c>
       <c r="E135" s="15" t="n">
-        <v>1782663.38</v>
+        <v>390804.18</v>
       </c>
       <c r="F135" s="15" t="n">
-        <v>10869.89865853659</v>
+        <v>13026.806</v>
       </c>
     </row>
     <row r="136">
@@ -4045,20 +4045,20 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C136" s="10" t="n">
-        <v>214</v>
+        <v>90</v>
       </c>
       <c r="D136" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E136" s="11" t="n">
-        <v>2116288.22</v>
+        <v>719529.78</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>9889.197289719626</v>
+        <v>7994.775333333334</v>
       </c>
     </row>
     <row r="137">
@@ -4069,20 +4069,20 @@
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C137" s="14" t="n">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="D137" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>266105.81</v>
+        <v>1837842.87</v>
       </c>
       <c r="F137" s="15" t="n">
-        <v>19007.55785714286</v>
+        <v>11005.0471257485</v>
       </c>
     </row>
     <row r="138">
@@ -4093,68 +4093,68 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>283</v>
+        <v>216</v>
       </c>
       <c r="D138" s="10" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E138" s="11" t="n">
-        <v>4076611.18</v>
+        <v>2134126.21</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>14404.98650176679</v>
+        <v>9880.213935185186</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C139" s="14" t="n">
-        <v>432</v>
+        <v>15</v>
       </c>
       <c r="D139" s="14" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E139" s="15" t="n">
-        <v>2889620.48</v>
+        <v>340756.66</v>
       </c>
       <c r="F139" s="15" t="n">
-        <v>6688.936296296296</v>
+        <v>22717.11066666667</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>370</v>
+        <v>283</v>
       </c>
       <c r="D140" s="10" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E140" s="11" t="n">
-        <v>1385427.19</v>
+        <v>4076611.18</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>3744.397810810811</v>
+        <v>14404.98650176679</v>
       </c>
     </row>
     <row r="141">
@@ -4165,20 +4165,20 @@
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C141" s="14" t="n">
-        <v>239</v>
+        <v>453</v>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E141" s="15" t="n">
-        <v>2066623.44</v>
+        <v>3045081.45</v>
       </c>
       <c r="F141" s="15" t="n">
-        <v>8646.959999999999</v>
+        <v>6722.034105960265</v>
       </c>
     </row>
     <row r="142">
@@ -4189,20 +4189,20 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>202</v>
+        <v>377</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E142" s="11" t="n">
-        <v>1813262.51</v>
+        <v>1437875.26</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>8976.547079207921</v>
+        <v>3813.992732095491</v>
       </c>
     </row>
     <row r="143">
@@ -4213,68 +4213,68 @@
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C143" s="14" t="n">
-        <v>527</v>
+        <v>243</v>
       </c>
       <c r="D143" s="14" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="E143" s="15" t="n">
-        <v>3687911.57</v>
+        <v>2114999.32</v>
       </c>
       <c r="F143" s="15" t="n">
-        <v>6997.934667931689</v>
+        <v>8703.700905349793</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C144" s="10" t="n">
-        <v>3250</v>
+        <v>204</v>
       </c>
       <c r="D144" s="10" t="n">
-        <v>297</v>
+        <v>8</v>
       </c>
       <c r="E144" s="11" t="n">
-        <v>20421616.5</v>
+        <v>1824281.82</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>6283.574307692308</v>
+        <v>8942.55794117647</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C145" s="14" t="n">
-        <v>126</v>
+        <v>530</v>
       </c>
       <c r="D145" s="14" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="E145" s="15" t="n">
-        <v>588325.26</v>
+        <v>3751709.6</v>
       </c>
       <c r="F145" s="15" t="n">
-        <v>4669.248095238096</v>
+        <v>7078.697358490566</v>
       </c>
     </row>
     <row r="146">
@@ -4285,20 +4285,20 @@
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>5083</v>
+        <v>3557</v>
       </c>
       <c r="D146" s="10" t="n">
-        <v>85</v>
+        <v>301</v>
       </c>
       <c r="E146" s="11" t="n">
-        <v>37598998.04</v>
+        <v>22365517.19</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>7397.009254377336</v>
+        <v>6287.747312341861</v>
       </c>
     </row>
     <row r="147">
@@ -4309,20 +4309,20 @@
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C147" s="14" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="D147" s="14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>1588664.9</v>
+        <v>614934.03</v>
       </c>
       <c r="F147" s="15" t="n">
-        <v>12127.21297709924</v>
+        <v>4488.569562043795</v>
       </c>
     </row>
     <row r="148">
@@ -4333,20 +4333,20 @@
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>4264</v>
+        <v>5157</v>
       </c>
       <c r="D148" s="10" t="n">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="E148" s="11" t="n">
-        <v>43242074.99</v>
+        <v>38360804.42</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>10141.19957551595</v>
+        <v>7438.589183633896</v>
       </c>
     </row>
     <row r="149">
@@ -4357,20 +4357,20 @@
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C149" s="14" t="n">
-        <v>5381</v>
+        <v>136</v>
       </c>
       <c r="D149" s="14" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="E149" s="15" t="n">
-        <v>67683411.13</v>
+        <v>1633044.23</v>
       </c>
       <c r="F149" s="15" t="n">
-        <v>12578.22173016168</v>
+        <v>12007.67816176471</v>
       </c>
     </row>
     <row r="150">
@@ -4381,68 +4381,68 @@
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>9771</v>
+        <v>4326</v>
       </c>
       <c r="D150" s="10" t="n">
-        <v>271</v>
+        <v>66</v>
       </c>
       <c r="E150" s="11" t="n">
-        <v>104407706.15</v>
+        <v>44158497.01</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>10685.46782826732</v>
+        <v>10207.69695099399</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C151" s="14" t="n">
-        <v>1709</v>
+        <v>5451</v>
       </c>
       <c r="D151" s="14" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E151" s="15" t="n">
-        <v>12493442.76</v>
+        <v>68939891.37</v>
       </c>
       <c r="F151" s="15" t="n">
-        <v>7310.381954359274</v>
+        <v>12647.20076499725</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C152" s="10" t="n">
-        <v>281</v>
+        <v>9853</v>
       </c>
       <c r="D152" s="10" t="n">
-        <v>8</v>
+        <v>274</v>
       </c>
       <c r="E152" s="11" t="n">
-        <v>1708212.43</v>
+        <v>105724138.38</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>6079.047793594305</v>
+        <v>10730.14699888359</v>
       </c>
     </row>
     <row r="153">
@@ -4453,20 +4453,20 @@
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C153" s="14" t="n">
-        <v>3987</v>
+        <v>1782</v>
       </c>
       <c r="D153" s="14" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>23716548.59</v>
+        <v>13078992.65</v>
       </c>
       <c r="F153" s="15" t="n">
-        <v>5948.469673940306</v>
+        <v>7339.502048260382</v>
       </c>
     </row>
     <row r="154">
@@ -4477,20 +4477,20 @@
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C154" s="10" t="n">
-        <v>560</v>
+        <v>285</v>
       </c>
       <c r="D154" s="10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E154" s="11" t="n">
-        <v>5611761.09</v>
+        <v>1755125.14</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>10021.00194642857</v>
+        <v>6158.333824561403</v>
       </c>
     </row>
     <row r="155">
@@ -4501,20 +4501,20 @@
       </c>
       <c r="B155" s="13" t="inlineStr">
         <is>
-          <t>21-25</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C155" s="14" t="n">
-        <v>89</v>
+        <v>4038</v>
       </c>
       <c r="D155" s="14" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="E155" s="15" t="n">
-        <v>1575111.8</v>
+        <v>24187668.59</v>
       </c>
       <c r="F155" s="15" t="n">
-        <v>17697.88539325843</v>
+        <v>5990.012033184745</v>
       </c>
     </row>
     <row r="156">
@@ -4525,68 +4525,68 @@
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>3305</v>
+        <v>567</v>
       </c>
       <c r="D156" s="10" t="n">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="E156" s="11" t="n">
-        <v>31532491.65</v>
+        <v>5720162.35</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>9540.84467473525</v>
+        <v>10088.46975308642</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>21-25</t>
         </is>
       </c>
       <c r="C157" s="14" t="n">
-        <v>164</v>
+        <v>90</v>
       </c>
       <c r="D157" s="14" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E157" s="15" t="n">
-        <v>1823327.87</v>
+        <v>1601025.28</v>
       </c>
       <c r="F157" s="15" t="n">
-        <v>11117.85286585366</v>
+        <v>17789.16977777778</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>24</v>
+        <v>3333</v>
       </c>
       <c r="D158" s="10" t="n">
-        <v>2</v>
+        <v>125</v>
       </c>
       <c r="E158" s="11" t="n">
-        <v>312025.7</v>
+        <v>31908003.2</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>13001.07083333333</v>
+        <v>9573.358295829583</v>
       </c>
     </row>
     <row r="159">
@@ -4597,20 +4597,20 @@
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C159" s="14" t="n">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="D159" s="14" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E159" s="15" t="n">
-        <v>252137.02</v>
+        <v>1926789.58</v>
       </c>
       <c r="F159" s="15" t="n">
-        <v>10962.47913043478</v>
+        <v>11010.22617142857</v>
       </c>
     </row>
     <row r="160">
@@ -4621,20 +4621,20 @@
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D160" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E160" s="11" t="n">
-        <v>448373.73</v>
+        <v>342409.39</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>12810.678</v>
+        <v>13169.59192307692</v>
       </c>
     </row>
     <row r="161">
@@ -4645,68 +4645,68 @@
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C161" s="14" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D161" s="14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E161" s="15" t="n">
-        <v>270105.97</v>
+        <v>264805.79</v>
       </c>
       <c r="F161" s="15" t="n">
-        <v>5627.207708333334</v>
+        <v>11033.57458333333</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Urbanismo e Licenciamento</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C162" s="10" t="n">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="D162" s="10" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E162" s="11" t="n">
-        <v>596814.74</v>
+        <v>463210.65</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>4005.468053691275</v>
+        <v>12866.9625</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="12" t="inlineStr">
         <is>
-          <t>Secretaria de Urbanismo e Licenciamento</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B163" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C163" s="14" t="n">
-        <v>258</v>
+        <v>49</v>
       </c>
       <c r="D163" s="14" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E163" s="15" t="n">
-        <v>1219057.68</v>
+        <v>271605.97</v>
       </c>
       <c r="F163" s="15" t="n">
-        <v>4725.02976744186</v>
+        <v>5542.978979591838</v>
       </c>
     </row>
     <row r="164">
@@ -4717,20 +4717,20 @@
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C164" s="10" t="n">
-        <v>438</v>
+        <v>149</v>
       </c>
       <c r="D164" s="10" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E164" s="11" t="n">
-        <v>2941872.34</v>
+        <v>596814.74</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>6716.603515981735</v>
+        <v>4005.468053691275</v>
       </c>
     </row>
     <row r="165">
@@ -4741,20 +4741,20 @@
       </c>
       <c r="B165" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C165" s="14" t="n">
-        <v>534</v>
+        <v>258</v>
       </c>
       <c r="D165" s="14" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E165" s="15" t="n">
-        <v>3538856.94</v>
+        <v>1219057.68</v>
       </c>
       <c r="F165" s="15" t="n">
-        <v>6627.072921348315</v>
+        <v>4725.02976744186</v>
       </c>
     </row>
     <row r="166">
@@ -4765,20 +4765,20 @@
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C166" s="10" t="n">
-        <v>74</v>
+        <v>438</v>
       </c>
       <c r="D166" s="10" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="E166" s="11" t="n">
-        <v>577087.41</v>
+        <v>2941872.34</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>7798.478513513514</v>
+        <v>6716.603515981735</v>
       </c>
     </row>
     <row r="167">
@@ -4789,68 +4789,68 @@
       </c>
       <c r="B167" s="13" t="inlineStr">
         <is>
-          <t>30+</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C167" s="14" t="n">
-        <v>1010</v>
+        <v>534</v>
       </c>
       <c r="D167" s="14" t="n">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="E167" s="15" t="n">
-        <v>6746352.86</v>
+        <v>3538856.94</v>
       </c>
       <c r="F167" s="15" t="n">
-        <v>6679.557287128713</v>
+        <v>6627.072921348315</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Urbanismo e Licenciamento</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>0-5</t>
+          <t>26-30</t>
         </is>
       </c>
       <c r="C168" s="10" t="n">
-        <v>1293</v>
+        <v>74</v>
       </c>
       <c r="D168" s="10" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E168" s="11" t="n">
-        <v>8484242.359999999</v>
+        <v>577087.41</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>6561.672358855375</v>
+        <v>7798.478513513514</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="12" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Urbanismo e Licenciamento</t>
         </is>
       </c>
       <c r="B169" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>30+</t>
         </is>
       </c>
       <c r="C169" s="14" t="n">
-        <v>562</v>
+        <v>1010</v>
       </c>
       <c r="D169" s="14" t="n">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="E169" s="15" t="n">
-        <v>3476475.03</v>
+        <v>6746352.86</v>
       </c>
       <c r="F169" s="15" t="n">
-        <v>6185.898629893238</v>
+        <v>6679.557287128713</v>
       </c>
     </row>
     <row r="170">
@@ -4861,20 +4861,20 @@
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>0-5</t>
         </is>
       </c>
       <c r="C170" s="10" t="n">
-        <v>2278</v>
+        <v>1358</v>
       </c>
       <c r="D170" s="10" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E170" s="11" t="n">
-        <v>18493966.78</v>
+        <v>8840958.119999999</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>8118.510438981563</v>
+        <v>6510.278438880707</v>
       </c>
     </row>
     <row r="171">
@@ -4885,20 +4885,20 @@
       </c>
       <c r="B171" s="13" t="inlineStr">
         <is>
-          <t>16-20</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C171" s="14" t="n">
-        <v>1038</v>
+        <v>582</v>
       </c>
       <c r="D171" s="14" t="n">
         <v>26</v>
       </c>
       <c r="E171" s="15" t="n">
-        <v>9662755.24</v>
+        <v>3611881.1</v>
       </c>
       <c r="F171" s="15" t="n">
-        <v>9309.012755298652</v>
+        <v>6205.981271477664</v>
       </c>
     </row>
     <row r="172">
@@ -4909,20 +4909,20 @@
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>26-30</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C172" s="10" t="n">
-        <v>55</v>
+        <v>2324</v>
       </c>
       <c r="D172" s="10" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E172" s="11" t="n">
-        <v>674837.08</v>
+        <v>18958024.9</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>12269.76509090909</v>
+        <v>8157.497805507744</v>
       </c>
     </row>
     <row r="173">
@@ -4933,24 +4933,72 @@
       </c>
       <c r="B173" s="13" t="inlineStr">
         <is>
+          <t>16-20</t>
+        </is>
+      </c>
+      <c r="C173" s="14" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D173" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>9866426.33</v>
+      </c>
+      <c r="F173" s="15" t="n">
+        <v>9325.544735349717</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="8" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B174" s="9" t="inlineStr">
+        <is>
+          <t>26-30</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="D174" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>674837.08</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>12269.76509090909</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B175" s="13" t="inlineStr">
+        <is>
           <t>30+</t>
         </is>
       </c>
-      <c r="C173" s="14" t="n">
-        <v>2562</v>
-      </c>
-      <c r="D173" s="14" t="n">
-        <v>175</v>
-      </c>
-      <c r="E173" s="15" t="n">
-        <v>19986622.98</v>
-      </c>
-      <c r="F173" s="15" t="n">
-        <v>7801.179929742389</v>
+      <c r="C175" s="14" t="n">
+        <v>2576</v>
+      </c>
+      <c r="D175" s="14" t="n">
+        <v>176</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>20214783.64</v>
+      </c>
+      <c r="F175" s="15" t="n">
+        <v>7847.353897515528</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F173"/>
+  <autoFilter ref="A1:F175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>